--- a/paper_case_manuel_instance.xlsx
+++ b/paper_case_manuel_instance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flights" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Flights" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gates" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/paper_case_manuel_instance.xlsx
+++ b/paper_case_manuel_instance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Flights" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flights" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1316</v>
+        <v>1256</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>632</v>
+        <v>572</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
